--- a/samples/ss_sktni_ingest.xlsx
+++ b/samples/ss_sktni_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_sktni_ingest.xlsx
+++ b/samples/ss_sktni_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Sukatani 500/150 kV</t>
+          <t>IBT 1 Sukatani 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -734,31 +730,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New Sukatani (bus 150 kV)</t>
+          <t>IBT 2 Sukatani 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 SKTNI7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SKTNI7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>NSKTN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -787,12 +797,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sukatani (bus 150 kV)</t>
+          <t>New Sukatani (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>NSKTN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -801,7 +811,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -813,11 +823,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Trf 1,2</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -827,14 +833,10 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -848,12 +850,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mitsuda</t>
+          <t>Sukatani (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MTSDA</t>
+          <t>SKTNI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -862,7 +864,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -874,7 +876,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Trf 1,2</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -884,10 +890,14 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -901,12 +911,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kesambi Baru</t>
+          <t>Mitsuda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KSBRU</t>
+          <t>MTSDA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -937,14 +947,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -958,12 +964,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dawuan</t>
+          <t>Kesambi Baru</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DWUAN</t>
+          <t>KSBRU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -972,7 +978,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -994,10 +1000,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1011,12 +1021,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bekasi (UP2B Jakban)</t>
+          <t>Dawuan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>DWUAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1025,7 +1035,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1037,22 +1047,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Bekasi 1,3 - Cibinong 3</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1072,12 +1074,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
+          <t>Bekasi (UP2B Jakban)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TTJBR</t>
+          <t>BKASI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1086,7 +1088,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1100,7 +1102,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
+          <t>batas ke Subsistem Bekasi 1,3 - Cibinong 3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1133,12 +1135,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indramayu Baru (SS Cibatu 3,4)</t>
+          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IDBRU</t>
+          <t>TTJBR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1194,12 +1196,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maligi / Katomukti (SS Cibatu 3,4)</t>
+          <t>Indramayu Baru (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MLIGI</t>
+          <t>IDBRU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1248,6 +1250,67 @@
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Maligi / Katomukti (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MLIGI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1892,12 +1955,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat potensi gangguan pasokan permanen KTT Multistrada pada saat pekerjaan Rekonduktoring SUTT 150 kV Sukatani Gobel - Kosambi Baru 1,2 yang rencana total durasi pekerjaan selama 18 bulan apabila terjadi N-2 IBT 1,2 GITET Sukatani atau SUTT 150 kV New Sukatani - Sukatani Gobel</t>
+          <t>[N-2] Terdapat potensi gangguan pasokan permanen KTT Multistrada pada saat pekerjaan Rekonduktoring SUTT 150 kV Sukatani Gobel - Kosambi Baru 1,2 yang rencana total durasi pekerjaan selama 18 bulan apabila terjadi N-2 IBT 1,2 GITET Sukatani atau SUTT 150 kV New Sukatani - Sukatani Gobel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/samples/ss_sktni_ingest.xlsx
+++ b/samples/ss_sktni_ingest.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1904,6 +1905,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bekasi (bus 150 kV)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NSKTN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IDBRU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Indramayu Baru (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MTSDA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MLIGI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Maligi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MTSDA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TTJBR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tegal Tanjung Baru</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MTSDA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
